--- a/script/Protocol Core Trt/Protocol_Core_ trt_list.xlsx
+++ b/script/Protocol Core Trt/Protocol_Core_ trt_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\script\Protocol Core Trt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8243F8FF-8AA9-4B4A-A897-DF6D44BC7DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61BFF4E-15E3-4883-A228-CF49A93C0DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -219,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -230,7 +230,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -593,7 +592,7 @@
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="1"/>

--- a/script/Protocol Core Trt/Protocol_Core_ trt_list.xlsx
+++ b/script/Protocol Core Trt/Protocol_Core_ trt_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\script\Protocol Core Trt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61BFF4E-15E3-4883-A228-CF49A93C0DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF55FFF-3107-4888-80E2-12CD3D5FB625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Nome trt</t>
   </si>
@@ -115,6 +115,12 @@
   </si>
   <si>
     <t>Libreria per la gestione dell'Autenticazione</t>
+  </si>
+  <si>
+    <t>YAX3MDEMOLIB</t>
+  </si>
+  <si>
+    <t>gestione Demo</t>
   </si>
 </sst>
 </file>
@@ -652,8 +658,12 @@
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
+      <c r="A16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">

--- a/script/Protocol Core Trt/Protocol_Core_ trt_list.xlsx
+++ b/script/Protocol Core Trt/Protocol_Core_ trt_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\script\Protocol Core Trt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF55FFF-3107-4888-80E2-12CD3D5FB625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EDB05B-8B57-4CF1-A77C-753FB976D69C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="2550" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Nome trt</t>
   </si>
@@ -93,9 +93,6 @@
     <t>Libreria per serializzazione json</t>
   </si>
   <si>
-    <t>Libreria per gestione selezioni(custom,multicustom/ad oggetto)</t>
-  </si>
-  <si>
     <t>Gestione servizi REST</t>
   </si>
   <si>
@@ -120,7 +117,16 @@
     <t>YAX3MDEMOLIB</t>
   </si>
   <si>
-    <t>gestione Demo</t>
+    <t>YAX3MACTIONS</t>
+  </si>
+  <si>
+    <t>Libreria per gestione azioni secondarie</t>
+  </si>
+  <si>
+    <t>Libreria per gestione selezioni(custom,multicustom/ad oggetto/consultazioni/gestione asterisco)</t>
+  </si>
+  <si>
+    <t>Gestione Demo</t>
   </si>
 </sst>
 </file>
@@ -144,15 +150,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -221,20 +233,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -527,16 +566,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -544,137 +583,157 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="9"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
